--- a/2023-10 A小区1单元示例.xlsx
+++ b/2023-10 A小区1单元示例.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="131">
+  <si>
+    <t>备注信息</t>
+  </si>
   <si>
     <t>计费号</t>
   </si>
@@ -38,6 +41,9 @@
   </si>
   <si>
     <t>2023-08</t>
+  </si>
+  <si>
+    <t>无</t>
   </si>
   <si>
     <t>442667</t>
@@ -1406,10 +1412,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1434,784 +1440,877 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2">
+        <v>14</v>
+      </c>
+      <c r="I2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3">
+        <v>12</v>
+      </c>
+      <c r="I3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>22</v>
+      </c>
+      <c r="I6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7">
+        <v>28</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9">
+        <v>24</v>
+      </c>
+      <c r="I9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10">
+        <v>7</v>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11">
+        <v>19</v>
+      </c>
+      <c r="I11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12">
+        <v>26</v>
+      </c>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12">
+        <v>18</v>
+      </c>
+      <c r="I12">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+      <c r="I13">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14">
+        <v>26</v>
+      </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14">
+        <v>18</v>
+      </c>
+      <c r="I14">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15">
+        <v>11</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16">
+        <v>11</v>
+      </c>
+      <c r="G16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17">
+        <v>29</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17">
+        <v>21</v>
+      </c>
+      <c r="I17">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18">
+        <v>11</v>
+      </c>
+      <c r="I18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19">
+        <v>4</v>
+      </c>
+      <c r="I19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20">
+        <v>17</v>
+      </c>
+      <c r="G20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20">
+        <v>9</v>
+      </c>
+      <c r="I20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21">
+        <v>11</v>
+      </c>
+      <c r="G21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="I21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22">
+        <v>11</v>
+      </c>
+      <c r="I22">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23">
+        <v>5</v>
+      </c>
+      <c r="I23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24">
+        <v>16</v>
+      </c>
+      <c r="G24" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24">
+        <v>8</v>
+      </c>
+      <c r="I24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25">
+        <v>33</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25">
+        <v>25</v>
+      </c>
+      <c r="I25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>14</v>
-      </c>
-      <c r="H2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
+      <c r="I26">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27" t="s">
+        <v>114</v>
+      </c>
+      <c r="F27">
+        <v>21</v>
+      </c>
+      <c r="G27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27">
+        <v>13</v>
+      </c>
+      <c r="I27">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" t="s">
+        <v>117</v>
+      </c>
+      <c r="E28" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>12</v>
-      </c>
-      <c r="H3">
+      <c r="G28" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28">
+        <v>7</v>
+      </c>
+      <c r="I28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4">
+      <c r="G29" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29">
+        <v>7</v>
+      </c>
+      <c r="I29">
         <v>10</v>
       </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5">
-        <v>18</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-      <c r="H5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>22</v>
-      </c>
-      <c r="H6">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <v>28</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>20</v>
-      </c>
-      <c r="H7">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8">
-        <v>20</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>12</v>
-      </c>
-      <c r="H8">
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" t="s">
+        <v>124</v>
+      </c>
+      <c r="D30" t="s">
+        <v>125</v>
+      </c>
+      <c r="E30" t="s">
+        <v>126</v>
+      </c>
+      <c r="F30">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30">
+        <v>6</v>
+      </c>
+      <c r="I30">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" t="s">
+        <v>130</v>
+      </c>
+      <c r="F31">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9">
-        <v>32</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
-        <v>24</v>
-      </c>
-      <c r="H9">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10">
-        <v>15</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
+      <c r="G31" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31">
         <v>7</v>
       </c>
-      <c r="H10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11">
-        <v>27</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>19</v>
-      </c>
-      <c r="H11">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12">
-        <v>26</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>18</v>
-      </c>
-      <c r="H12">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-      <c r="H13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14">
-        <v>26</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14">
-        <v>18</v>
-      </c>
-      <c r="H14">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15">
-        <v>11</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15">
-        <v>3</v>
-      </c>
-      <c r="H15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>3</v>
-      </c>
-      <c r="H16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17">
-        <v>29</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>21</v>
-      </c>
-      <c r="H17">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18">
-        <v>19</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>11</v>
-      </c>
-      <c r="H18">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19">
-        <v>12</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
-        <v>4</v>
-      </c>
-      <c r="H19">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>81</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20">
-        <v>17</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20">
-        <v>9</v>
-      </c>
-      <c r="H20">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" t="s">
-        <v>85</v>
-      </c>
-      <c r="B21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21">
-        <v>3</v>
-      </c>
-      <c r="H21">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" t="s">
-        <v>92</v>
-      </c>
-      <c r="E22">
-        <v>19</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22">
-        <v>11</v>
-      </c>
-      <c r="H22">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" t="s">
-        <v>93</v>
-      </c>
-      <c r="B23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" t="s">
-        <v>96</v>
-      </c>
-      <c r="E23">
-        <v>13</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-      <c r="H23">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" t="s">
-        <v>97</v>
-      </c>
-      <c r="B24" t="s">
-        <v>98</v>
-      </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24">
-        <v>16</v>
-      </c>
-      <c r="F24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24">
-        <v>8</v>
-      </c>
-      <c r="H24">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25">
-        <v>33</v>
-      </c>
-      <c r="F25" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25">
-        <v>25</v>
-      </c>
-      <c r="H25">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>105</v>
-      </c>
-      <c r="B26" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" t="s">
-        <v>108</v>
-      </c>
-      <c r="E26">
-        <v>18</v>
-      </c>
-      <c r="F26" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26">
-        <v>10</v>
-      </c>
-      <c r="H26">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" t="s">
-        <v>109</v>
-      </c>
-      <c r="B27" t="s">
-        <v>110</v>
-      </c>
-      <c r="C27" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" t="s">
-        <v>112</v>
-      </c>
-      <c r="E27">
-        <v>21</v>
-      </c>
-      <c r="F27" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27">
-        <v>13</v>
-      </c>
-      <c r="H27">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" t="s">
-        <v>113</v>
-      </c>
-      <c r="B28" t="s">
-        <v>114</v>
-      </c>
-      <c r="C28" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" t="s">
-        <v>116</v>
-      </c>
-      <c r="E28">
-        <v>15</v>
-      </c>
-      <c r="F28" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28">
-        <v>7</v>
-      </c>
-      <c r="H28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" t="s">
-        <v>117</v>
-      </c>
-      <c r="B29" t="s">
-        <v>118</v>
-      </c>
-      <c r="C29" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" t="s">
-        <v>120</v>
-      </c>
-      <c r="E29">
-        <v>15</v>
-      </c>
-      <c r="F29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29">
-        <v>7</v>
-      </c>
-      <c r="H29">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" t="s">
-        <v>121</v>
-      </c>
-      <c r="B30" t="s">
-        <v>122</v>
-      </c>
-      <c r="C30" t="s">
-        <v>123</v>
-      </c>
-      <c r="D30" t="s">
-        <v>124</v>
-      </c>
-      <c r="E30">
-        <v>14</v>
-      </c>
-      <c r="F30" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30">
-        <v>6</v>
-      </c>
-      <c r="H30">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" t="s">
-        <v>125</v>
-      </c>
-      <c r="B31" t="s">
-        <v>126</v>
-      </c>
-      <c r="C31" t="s">
-        <v>127</v>
-      </c>
-      <c r="D31" t="s">
-        <v>128</v>
-      </c>
-      <c r="E31">
-        <v>15</v>
-      </c>
-      <c r="F31" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31">
-        <v>7</v>
-      </c>
-      <c r="H31">
+      <c r="I31">
         <v>10</v>
       </c>
     </row>
@@ -2219,7 +2318,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 A2:D31 F2:F31 H2:H31" numberStoredAsText="1"/>
+    <ignoredError sqref="H2:I31 B2:E31 B1:I1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/2023-10 A小区1单元示例.xlsx
+++ b/2023-10 A小区1单元示例.xlsx
@@ -4,12 +4,25 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12525"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -412,7 +425,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1027,8 +1040,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1437,7 +1451,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -1461,6 +1475,7 @@
         <v>13</v>
       </c>
       <c r="F2">
+        <f>I2+5</f>
         <v>22</v>
       </c>
       <c r="G2" t="s">
@@ -1490,6 +1505,7 @@
         <v>18</v>
       </c>
       <c r="F3">
+        <f t="shared" ref="F3:F31" si="0">I3+5</f>
         <v>20</v>
       </c>
       <c r="G3" t="s">
@@ -1519,6 +1535,7 @@
         <v>22</v>
       </c>
       <c r="F4">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="G4" t="s">
@@ -1548,6 +1565,7 @@
         <v>26</v>
       </c>
       <c r="F5">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="G5" t="s">
@@ -1577,6 +1595,7 @@
         <v>30</v>
       </c>
       <c r="F6">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="G6" t="s">
@@ -1606,6 +1625,7 @@
         <v>34</v>
       </c>
       <c r="F7">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="G7" t="s">
@@ -1635,6 +1655,7 @@
         <v>38</v>
       </c>
       <c r="F8">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="G8" t="s">
@@ -1664,6 +1685,7 @@
         <v>42</v>
       </c>
       <c r="F9">
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="G9" t="s">
@@ -1693,6 +1715,7 @@
         <v>46</v>
       </c>
       <c r="F10">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="G10" t="s">
@@ -1722,6 +1745,7 @@
         <v>50</v>
       </c>
       <c r="F11">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="G11" t="s">
@@ -1751,6 +1775,7 @@
         <v>54</v>
       </c>
       <c r="F12">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="G12" t="s">
@@ -1780,6 +1805,7 @@
         <v>58</v>
       </c>
       <c r="F13">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="G13" t="s">
@@ -1809,6 +1835,7 @@
         <v>62</v>
       </c>
       <c r="F14">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="G14" t="s">
@@ -1838,6 +1865,7 @@
         <v>66</v>
       </c>
       <c r="F15">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="G15" t="s">
@@ -1867,6 +1895,7 @@
         <v>70</v>
       </c>
       <c r="F16">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="G16" t="s">
@@ -1896,6 +1925,7 @@
         <v>74</v>
       </c>
       <c r="F17">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="G17" t="s">
@@ -1925,6 +1955,7 @@
         <v>78</v>
       </c>
       <c r="F18">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="G18" t="s">
@@ -1954,6 +1985,7 @@
         <v>82</v>
       </c>
       <c r="F19">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="G19" t="s">
@@ -1983,6 +2015,7 @@
         <v>86</v>
       </c>
       <c r="F20">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="G20" t="s">
@@ -2012,6 +2045,7 @@
         <v>90</v>
       </c>
       <c r="F21">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="G21" t="s">
@@ -2041,6 +2075,7 @@
         <v>94</v>
       </c>
       <c r="F22">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="G22" t="s">
@@ -2070,6 +2105,7 @@
         <v>98</v>
       </c>
       <c r="F23">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="G23" t="s">
@@ -2099,6 +2135,7 @@
         <v>102</v>
       </c>
       <c r="F24">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="G24" t="s">
@@ -2128,6 +2165,7 @@
         <v>106</v>
       </c>
       <c r="F25">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="G25" t="s">
@@ -2157,6 +2195,7 @@
         <v>110</v>
       </c>
       <c r="F26">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="G26" t="s">
@@ -2186,6 +2225,7 @@
         <v>114</v>
       </c>
       <c r="F27">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="G27" t="s">
@@ -2215,6 +2255,7 @@
         <v>118</v>
       </c>
       <c r="F28">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="G28" t="s">
@@ -2244,6 +2285,7 @@
         <v>122</v>
       </c>
       <c r="F29">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="G29" t="s">
@@ -2273,6 +2315,7 @@
         <v>126</v>
       </c>
       <c r="F30">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="G30" t="s">
@@ -2302,6 +2345,7 @@
         <v>130</v>
       </c>
       <c r="F31">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="G31" t="s">
@@ -2318,7 +2362,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="H2:I31 B2:E31 B1:I1" numberStoredAsText="1"/>
+    <ignoredError sqref="B1:E1 G1 I1 B2:E31 H2:I31" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>